--- a/简易停.xlsx
+++ b/简易停.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\新建文件夹\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F88198F4-259E-4151-9623-7D4623B30862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{918F6752-29B6-4113-AE4D-4099982F7551}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26070" yWindow="2700" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-30" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="36">
   <si>
     <t>后台接口</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -39,35 +39,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>参数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/jyt/login</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>备注2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>/jyt/register</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">username:String,
-userpwd:String
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>/jyt/user_layout</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">token || cooking :String 
-username:String ,
-</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -79,26 +55,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>return Info</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Login 登录接口</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/manager/generate_invacode</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>{length：“邀请码长度”}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>返回一个邀请码，如：{“invacdoe”:"0xsdad"}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>方法</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -111,33 +71,215 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{token: String}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">username:String,
-userpwd:String
-userinvcode:Number
-email:String
+    <t>/jyt/manager/generate_invacode</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>请求参数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>示例</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+                    code: 200,
+                    data: {
+                        msg: 'layout路由',
+                        layout_route: [
+                            {
+                                meta: {
+                                    title: '后台管理',
+                                    icon: 'i-uim:box',
+                                    name: 'layout',
+                                    path: '/'
+                                },
+                                children: [
+                                    {
+                                        name: 'setting',
+                                        path: '/setting',
+                                        redirect: '/setting/menu_management',
+                                        meta: {
+                                            icon: 'i-ic:outline-settings',
+                                            title: '系统设置'
+                                        },
+                                        children: [
+                                            {
+                                                path: '/setting/menu_management',
+                                                component:'Setting/Menu_management/index.vue',
+                                                meta: {
+                                                    name: "menu_management",
+                                                    icon: 'i-subway:menu',
+                                                    title: '菜单管理'
+                                                }
+                                            },
+                                            {
+                                                path: '/setting/role_management',
+                                                component: 'Setting/Role_management/index.vue',
+                                                meta: {
+                                                    name: "role_management",
+                                                    icon: 'i-oui:app-users-roles',
+                                                    title: '角色管理'
+                                                }
+                                            },
+                                            {
+                                                path: '/setting/user_management',
+                                                component: 'Setting/User_management/index.vue',
+                                                meta: {
+                                                    name: "user_management",
+                                                    icon: 'i-ri:user-5-fill',
+                                                    title: '用户管理'
+                                                }
+                                            }
+                                        ]
+                                    }
+                                ]
+                            },
+                            {
+                                meta: {
+                                    title: '小程序管理',
+                                    icon: 'i-solar:box-minimalistic-bold',
+                                    name: 'small_program'
+                                },
+                                children: []
+                            }
+                        ]
+                    }
+                })</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+                code: 200,
+                data: {
+                    msg: '登录成功',
+                    token: mock.Random.string('mixed', 10)
+                }
+            })</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+                code: 200,
+                data: {
+                    msg: '注册成功',
+                }
+            })</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+                code: 200,
+                data: {
+                    msg: '密码重置成功,
+                }
+            })</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+                code: 200,
+                data: {
+                    msg: '邀请码生成成功,
+“invacdoe”:"0xsdad"
+                }
+            })</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>接口</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>后端测试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>as_user_account: "小菜1111"
+as_user_email: "2306400714@qq.com"
+as_user_invitation_code: "123456"
+as_user_password: "123456"
+as_user_current_password: "123456"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+as_user_email: "2306400714@qq.com"
+as_user_invitation_code: "123456"
+as_user_password: "123456"
 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>/jyt/forget_passwd</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>email: String,
- verfi_code: String,
-    new_passwd: String,</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/jyt/send_email</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>email:String</t>
+    <t xml:space="preserve">token || cooking :'xjkjkojdklasjdkjaskdljsakljd' 
+username:‘小菜521111’ ,
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>前端测试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>as_user_account: "2306400714@qq.com", as_user_password: "123465", 
+as_user_remember: "false"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>响应码</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/jyt/user/login</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/jyt/user/register</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/jyt/user/forget_passwd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/jyt/manager/update_role</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+as_user_emai: String</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+                code: 201,
+                data: {
+                    msg: '设置管理员成功,
+                }
+            })</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/jyt/manager/delete_user</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DELETE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{
+                code: 202,
+                data: {
+                    msg: '删除成功,
+                }
+            })</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -145,7 +287,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -181,13 +323,70 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <b/>
+      <i/>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="22"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="22"/>
       <color rgb="FFCE9178"/>
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="22"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="26"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -212,6 +411,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -225,27 +436,57 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -531,199 +772,308 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="3" width="20.625" customWidth="1"/>
-    <col min="4" max="4" width="32.25" customWidth="1"/>
-    <col min="5" max="5" width="20.625" customWidth="1"/>
+    <col min="1" max="1" width="20.625" customWidth="1"/>
+    <col min="2" max="2" width="66.375" customWidth="1"/>
+    <col min="3" max="3" width="111.5" customWidth="1"/>
+    <col min="4" max="4" width="60.875" customWidth="1"/>
+    <col min="5" max="5" width="64.625" customWidth="1"/>
     <col min="6" max="6" width="42.75" customWidth="1"/>
-    <col min="7" max="14" width="20.625" customWidth="1"/>
+    <col min="7" max="7" width="82.375" customWidth="1"/>
+    <col min="8" max="8" width="80.875" customWidth="1"/>
+    <col min="9" max="9" width="56.125" customWidth="1"/>
+    <col min="10" max="14" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" ht="69.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:9" s="1" customFormat="1" ht="69.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-    </row>
-    <row r="2" spans="1:7" s="1" customFormat="1" ht="108.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="6" t="s">
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+    </row>
+    <row r="2" spans="1:9" s="1" customFormat="1" ht="108.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+    </row>
+    <row r="3" spans="1:9" s="1" customFormat="1" ht="43.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+    </row>
+    <row r="4" spans="1:9" s="5" customFormat="1" ht="162.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" s="1" customFormat="1" ht="365.65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="9">
+        <v>1</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="13">
+        <v>200</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" s="1" customFormat="1" ht="322.89999999999998" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="9">
+        <v>2</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="9">
+        <v>200</v>
+      </c>
+      <c r="G6" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" s="1" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="9">
+        <v>3</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="13">
+        <v>200</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" s="1" customFormat="1" ht="308.64999999999998" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="9">
+        <v>4</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-    </row>
-    <row r="3" spans="1:7" s="1" customFormat="1" ht="43.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-    </row>
-    <row r="4" spans="1:7" s="1" customFormat="1" ht="43.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
+      <c r="C8" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="4"/>
+      <c r="F8" s="9">
+        <v>200</v>
+      </c>
+      <c r="G8" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="3" t="s">
+      <c r="I8" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" s="1" customFormat="1" ht="346.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="9">
+        <v>5</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="9">
+        <v>200</v>
+      </c>
+      <c r="G9" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="3"/>
-    </row>
-    <row r="5" spans="1:7" s="1" customFormat="1" ht="120" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="1">
+      <c r="H9" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" s="1" customFormat="1" ht="120" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="1">
-        <v>2</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="1">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" s="1" customFormat="1" ht="120" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="1">
-        <v>3</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" s="2"/>
-    </row>
-    <row r="8" spans="1:7" s="1" customFormat="1" ht="120" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="1">
-        <v>4</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" s="1" customFormat="1" ht="120" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="1">
-        <v>5</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9" s="1">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" s="1" customFormat="1" ht="120" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I9" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" s="1" customFormat="1" ht="120" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>6</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" s="1" customFormat="1" ht="120" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="9">
+        <v>200</v>
+      </c>
+      <c r="G10" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="H10" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" s="1" customFormat="1" ht="120" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>7</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" s="1" customFormat="1" ht="120" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11" s="9">
+        <v>200</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="H11" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I11" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" s="1" customFormat="1" ht="120" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:7" s="1" customFormat="1" ht="120" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" s="1" customFormat="1" ht="120" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:7" s="1" customFormat="1" ht="120" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" s="1" customFormat="1" ht="120" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:7" s="1" customFormat="1" ht="120" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" s="1" customFormat="1" ht="120" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:7" s="1" customFormat="1" ht="120" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" s="1" customFormat="1" ht="120" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
